--- a/marketing_forms/006_marketing_reach_evaluation_form--marketing_forms.xlsx
+++ b/marketing_forms/006_marketing_reach_evaluation_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bi_weekly'}</t>
+          <t>bi_weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'bi_weekly'}</t>
+          <t>bi weekly</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'channel_a'}</t>
+          <t>channel_a</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'channel_a'}</t>
+          <t>channel a</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'channel_b'}</t>
+          <t>channel_b</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'channel_b'}</t>
+          <t>channel b</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'channel_c'}</t>
+          <t>channel_c</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'channel_c'}</t>
+          <t>channel c</t>
         </is>
       </c>
     </row>
